--- a/testfiles/Real_Test.xlsx
+++ b/testfiles/Real_Test.xlsx
@@ -1,31 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Engine\NimbleAnalyzer2\testfiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB9E0001-935F-4199-9B82-233C2DA9700D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38970" yWindow="5370" windowWidth="28755" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="41475" yWindow="3600" windowWidth="28755" windowHeight="15345"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <calcPr calcId="162913" concurrentCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="35">
   <si>
     <t>Real Testcase testing every single import possible using "import" folder</t>
   </si>
@@ -43,13 +37,100 @@
   </si>
   <si>
     <t>Engineer</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>0430-100</t>
+  </si>
+  <si>
+    <t>Y:\Produktion\Prüffeld\Prüfprotokolle\Xe-µJoule</t>
+  </si>
+  <si>
+    <t>0430-101</t>
+  </si>
+  <si>
+    <t>0430-102</t>
+  </si>
+  <si>
+    <t>0430-103</t>
+  </si>
+  <si>
+    <t>0430-104</t>
+  </si>
+  <si>
+    <t>0430-105</t>
+  </si>
+  <si>
+    <t>0430-106</t>
+  </si>
+  <si>
+    <t>Adrian Jahraus</t>
+  </si>
+  <si>
+    <t>0430-107</t>
+  </si>
+  <si>
+    <t>0430-108</t>
+  </si>
+  <si>
+    <t>0430-109</t>
+  </si>
+  <si>
+    <t>0430-110</t>
+  </si>
+  <si>
+    <t>0430-111</t>
+  </si>
+  <si>
+    <t>0430-112</t>
+  </si>
+  <si>
+    <t>28.01.2026</t>
+  </si>
+  <si>
+    <t>29.01.2026</t>
+  </si>
+  <si>
+    <t>30.01.2026</t>
+  </si>
+  <si>
+    <t>31.01.2026</t>
+  </si>
+  <si>
+    <t>01.02.2026</t>
+  </si>
+  <si>
+    <t>02.02.2026</t>
+  </si>
+  <si>
+    <t>03.02.2026</t>
+  </si>
+  <si>
+    <t>04.02.2026</t>
+  </si>
+  <si>
+    <t>05.02.2026</t>
+  </si>
+  <si>
+    <t>06.02.2026</t>
+  </si>
+  <si>
+    <t>07.02.2026</t>
+  </si>
+  <si>
+    <t>08.02.2026</t>
+  </si>
+  <si>
+    <t>09.02.2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="1" x14ac:knownFonts="0">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -58,12 +139,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -78,20 +165,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium7"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -145,7 +231,7 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="DengXian Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -180,7 +266,7 @@
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="Yu Gothic"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="DengXian"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -359,12 +445,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="34.28515625" customWidth="1"/>
+    <col min="4" max="4" width="22.85546875" customWidth="1"/>
+    <col min="5" max="5" width="10.140625" bestFit="1" style="2" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -375,7 +466,7 @@
       <c r="B3" t="s">
         <v>2</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" t="s">
@@ -384,8 +475,154 @@
       <c r="E3" t="s">
         <v>4</v>
       </c>
+      <c r="F3" t="s">
+        <v>6</v>
+      </c>
       <c r="G3" t="s">
         <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" t="s">
+        <v>22</v>
+      </c>
+      <c r="G4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>23</v>
+      </c>
+      <c r="G5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>25</v>
+      </c>
+      <c r="G7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="G8" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="E13" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" t="s">
+        <v>32</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" t="s">
+        <v>34</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
